--- a/cp-short-description/ig/all-profiles.xlsx
+++ b/cp-short-description/ig/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24931" uniqueCount="1320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24931" uniqueCount="1321">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:20:15+00:00</t>
+    <t>2026-06-25T15:53:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -915,7 +915,7 @@
     <t>DocumentReference.description</t>
   </si>
   <si>
-    <t>Commentaire associé au document.</t>
+    <t>Description du document source, lisible par l'homme correspondant au commentaire associé au document</t>
   </si>
   <si>
     <t>Human-readable description of the source document.</t>
@@ -3876,6 +3876,9 @@
   </si>
   <si>
     <t>Target of the relationship</t>
+  </si>
+  <si>
+    <t>Commentaire associé au document.</t>
   </si>
   <si>
     <t>Document contenu.</t>
@@ -5612,7 +5615,7 @@
         <v>2</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="174">
@@ -5620,7 +5623,7 @@
         <v>4</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="175">
@@ -5636,7 +5639,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="177">
@@ -5644,7 +5647,7 @@
         <v>10</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="178">
@@ -5698,7 +5701,7 @@
         <v>23</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="185">
@@ -5742,7 +5745,7 @@
         <v>33</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="191">
@@ -74544,7 +74547,7 @@
         <v>98</v>
       </c>
       <c r="M659" t="s" s="2">
-        <v>283</v>
+        <v>1239</v>
       </c>
       <c r="N659" t="s" s="2">
         <v>284</v>
@@ -74758,7 +74761,7 @@
         <v>258</v>
       </c>
       <c r="M661" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="N661" t="s" s="2">
         <v>295</v>
@@ -75697,7 +75700,7 @@
         <v>320</v>
       </c>
       <c r="M670" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="N670" t="s" s="2">
         <v>322</v>
@@ -75804,7 +75807,7 @@
         <v>327</v>
       </c>
       <c r="M671" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="N671" t="s" s="2">
         <v>329</v>
@@ -76230,7 +76233,7 @@
         <v>355</v>
       </c>
       <c r="M675" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="N675" t="s" s="2">
         <v>357</v>
@@ -77233,7 +77236,7 @@
         <v>75</v>
       </c>
       <c r="AK684" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="685">
@@ -77338,7 +77341,7 @@
         <v>75</v>
       </c>
       <c r="AK685" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="686">
@@ -77551,7 +77554,7 @@
     </row>
     <row r="688">
       <c r="A688" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B688" t="s" s="2">
         <v>1094</v>
@@ -77654,7 +77657,7 @@
     </row>
     <row r="689">
       <c r="A689" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B689" t="s" s="2">
         <v>1097</v>
@@ -77759,7 +77762,7 @@
     </row>
     <row r="690">
       <c r="A690" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B690" t="s" s="2">
         <v>1098</v>
@@ -77862,7 +77865,7 @@
     </row>
     <row r="691">
       <c r="A691" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B691" t="s" s="2">
         <v>1099</v>
@@ -77965,7 +77968,7 @@
     </row>
     <row r="692">
       <c r="A692" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>1100</v>
@@ -78070,7 +78073,7 @@
     </row>
     <row r="693">
       <c r="A693" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B693" t="s" s="2">
         <v>1101</v>
@@ -78175,7 +78178,7 @@
     </row>
     <row r="694">
       <c r="A694" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B694" t="s" s="2">
         <v>1102</v>
@@ -78280,7 +78283,7 @@
     </row>
     <row r="695">
       <c r="A695" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B695" t="s" s="2">
         <v>1103</v>
@@ -78385,7 +78388,7 @@
     </row>
     <row r="696">
       <c r="A696" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B696" t="s" s="2">
         <v>1104</v>
@@ -78490,7 +78493,7 @@
     </row>
     <row r="697">
       <c r="A697" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B697" t="s" s="2">
         <v>1105</v>
@@ -78595,7 +78598,7 @@
     </row>
     <row r="698">
       <c r="A698" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B698" t="s" s="2">
         <v>1106</v>
@@ -78700,7 +78703,7 @@
     </row>
     <row r="699">
       <c r="A699" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B699" t="s" s="2">
         <v>1107</v>
@@ -78805,7 +78808,7 @@
     </row>
     <row r="700">
       <c r="A700" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B700" t="s" s="2">
         <v>1108</v>
@@ -78910,7 +78913,7 @@
     </row>
     <row r="701">
       <c r="A701" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B701" t="s" s="2">
         <v>1109</v>
@@ -79015,7 +79018,7 @@
     </row>
     <row r="702">
       <c r="A702" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B702" t="s" s="2">
         <v>1110</v>
@@ -79047,7 +79050,7 @@
         <v>176</v>
       </c>
       <c r="M702" t="s" s="2">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="N702" t="s" s="2">
         <v>178</v>
@@ -79120,7 +79123,7 @@
     </row>
     <row r="703">
       <c r="A703" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B703" t="s" s="2">
         <v>1112</v>
@@ -79134,7 +79137,7 @@
       </c>
       <c r="F703" s="2"/>
       <c r="G703" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="H703" t="s" s="2">
         <v>77</v>
@@ -79221,7 +79224,7 @@
     </row>
     <row r="704">
       <c r="A704" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B704" t="s" s="2">
         <v>1113</v>
@@ -79255,7 +79258,7 @@
         <v>1115</v>
       </c>
       <c r="M704" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="N704" t="s" s="2">
         <v>1117</v>
@@ -79321,18 +79324,18 @@
         <v>190</v>
       </c>
       <c r="AK704" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B705" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="C705" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="D705" s="2"/>
       <c r="E705" t="s" s="2">
@@ -79429,13 +79432,13 @@
     </row>
     <row r="706">
       <c r="A706" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B706" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="C706" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="D706" s="2"/>
       <c r="E706" t="s" s="2">
@@ -79532,13 +79535,13 @@
     </row>
     <row r="707">
       <c r="A707" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B707" t="s" s="2">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="C707" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D707" s="2"/>
       <c r="E707" t="s" s="2">
@@ -79578,7 +79581,7 @@
       </c>
       <c r="R707" s="2"/>
       <c r="S707" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="T707" t="s" s="2">
         <v>75</v>
@@ -79637,13 +79640,13 @@
     </row>
     <row r="708">
       <c r="A708" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B708" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C708" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D708" s="2"/>
       <c r="E708" t="s" s="2">
@@ -79703,7 +79706,7 @@
       </c>
       <c r="Z708" s="2"/>
       <c r="AA708" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="AB708" t="s" s="2">
         <v>75</v>
@@ -79738,16 +79741,16 @@
     </row>
     <row r="709">
       <c r="A709" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B709" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="C709" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D709" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="E709" t="s" s="2">
         <v>75</v>
@@ -79769,13 +79772,13 @@
         <v>75</v>
       </c>
       <c r="L709" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="M709" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="N709" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="O709" s="2"/>
       <c r="P709" s="2"/>
@@ -79843,16 +79846,16 @@
     </row>
     <row r="710">
       <c r="A710" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B710" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="C710" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D710" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="E710" t="s" s="2">
         <v>75</v>
@@ -79874,13 +79877,13 @@
         <v>75</v>
       </c>
       <c r="L710" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="M710" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="N710" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="O710" s="2"/>
       <c r="P710" s="2"/>
@@ -79948,10 +79951,10 @@
     </row>
     <row r="711">
       <c r="A711" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B711" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="C711" t="s" s="2">
         <v>1112</v>
@@ -79982,7 +79985,7 @@
         <v>187</v>
       </c>
       <c r="M711" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="N711" t="s" s="2">
         <v>189</v>
@@ -80053,16 +80056,16 @@
     </row>
     <row r="712">
       <c r="A712" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B712" t="s" s="2">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C712" t="s" s="2">
         <v>1112</v>
       </c>
       <c r="D712" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="E712" t="s" s="2">
         <v>75</v>
@@ -80084,10 +80087,10 @@
         <v>75</v>
       </c>
       <c r="L712" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="M712" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="N712" t="s" s="2">
         <v>989</v>
@@ -80158,13 +80161,13 @@
     </row>
     <row r="713">
       <c r="A713" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B713" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="C713" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="D713" s="2"/>
       <c r="E713" t="s" s="2">
@@ -80261,13 +80264,13 @@
     </row>
     <row r="714">
       <c r="A714" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B714" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C714" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="D714" s="2"/>
       <c r="E714" t="s" s="2">
@@ -80364,13 +80367,13 @@
     </row>
     <row r="715">
       <c r="A715" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B715" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C715" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="D715" s="2"/>
       <c r="E715" t="s" s="2">
@@ -80469,13 +80472,13 @@
     </row>
     <row r="716">
       <c r="A716" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B716" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="C716" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D716" s="2"/>
       <c r="E716" t="s" s="2">
@@ -80572,7 +80575,7 @@
     </row>
     <row r="717">
       <c r="A717" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B717" t="s" s="2">
         <v>1118</v>
@@ -80675,7 +80678,7 @@
     </row>
     <row r="718">
       <c r="A718" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B718" t="s" s="2">
         <v>1119</v>
@@ -80776,7 +80779,7 @@
     </row>
     <row r="719">
       <c r="A719" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B719" t="s" s="2">
         <v>1122</v>
@@ -80807,10 +80810,10 @@
         <v>75</v>
       </c>
       <c r="L719" t="s" s="2">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="M719" t="s" s="2">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="N719" t="s" s="2">
         <v>1121</v>
@@ -80881,7 +80884,7 @@
     </row>
     <row r="720">
       <c r="A720" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B720" t="s" s="2">
         <v>1125</v>
@@ -80915,7 +80918,7 @@
         <v>206</v>
       </c>
       <c r="M720" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="N720" t="s" s="2">
         <v>1121</v>
@@ -80986,7 +80989,7 @@
     </row>
     <row r="721">
       <c r="A721" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B721" t="s" s="2">
         <v>1127</v>
@@ -81018,7 +81021,7 @@
         <v>159</v>
       </c>
       <c r="M721" t="s" s="2">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="N721" t="s" s="2">
         <v>1129</v>
@@ -81091,7 +81094,7 @@
     </row>
     <row r="722">
       <c r="A722" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B722" t="s" s="2">
         <v>1133</v>
@@ -81123,7 +81126,7 @@
         <v>159</v>
       </c>
       <c r="M722" t="s" s="2">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="N722" t="s" s="2">
         <v>1135</v>
@@ -81198,7 +81201,7 @@
     </row>
     <row r="723">
       <c r="A723" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B723" t="s" s="2">
         <v>1141</v>
@@ -81230,7 +81233,7 @@
         <v>98</v>
       </c>
       <c r="M723" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="N723" t="s" s="2">
         <v>1143</v>
@@ -81303,7 +81306,7 @@
     </row>
     <row r="724">
       <c r="A724" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B724" t="s" s="2">
         <v>1146</v>
@@ -81335,7 +81338,7 @@
         <v>220</v>
       </c>
       <c r="M724" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="N724" t="s" s="2">
         <v>1148</v>
@@ -81354,7 +81357,7 @@
         <v>75</v>
       </c>
       <c r="T724" t="s" s="2">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="U724" t="s" s="2">
         <v>75</v>
@@ -81408,7 +81411,7 @@
     </row>
     <row r="725">
       <c r="A725" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B725" t="s" s="2">
         <v>1153</v>
@@ -81515,7 +81518,7 @@
     </row>
     <row r="726">
       <c r="A726" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B726" t="s" s="2">
         <v>1158</v>
@@ -81618,7 +81621,7 @@
     </row>
     <row r="727">
       <c r="A727" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B727" t="s" s="2">
         <v>1162</v>
@@ -81650,7 +81653,7 @@
         <v>355</v>
       </c>
       <c r="M727" t="s" s="2">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="N727" t="s" s="2">
         <v>1164</v>
@@ -81725,7 +81728,7 @@
     </row>
     <row r="728">
       <c r="A728" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B728" t="s" s="2">
         <v>1167</v>
@@ -81754,10 +81757,10 @@
         <v>85</v>
       </c>
       <c r="L728" t="s" s="2">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="M728" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="N728" t="s" s="2">
         <v>1171</v>
@@ -81832,13 +81835,13 @@
     </row>
     <row r="729">
       <c r="A729" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B729" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C729" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="D729" s="2"/>
       <c r="E729" t="s" s="2">
@@ -81935,13 +81938,13 @@
     </row>
     <row r="730">
       <c r="A730" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B730" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C730" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D730" s="2"/>
       <c r="E730" t="s" s="2">
@@ -82040,16 +82043,16 @@
     </row>
     <row r="731">
       <c r="A731" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B731" t="s" s="2">
+        <v>1298</v>
+      </c>
+      <c r="C731" t="s" s="2">
         <v>1297</v>
       </c>
-      <c r="C731" t="s" s="2">
-        <v>1296</v>
-      </c>
       <c r="D731" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="E731" t="s" s="2">
         <v>75</v>
@@ -82071,13 +82074,13 @@
         <v>75</v>
       </c>
       <c r="L731" t="s" s="2">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="M731" t="s" s="2">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="N731" t="s" s="2">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="O731" s="2"/>
       <c r="P731" s="2"/>
@@ -82145,13 +82148,13 @@
     </row>
     <row r="732">
       <c r="A732" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B732" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="C732" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="D732" s="2"/>
       <c r="E732" t="s" s="2">
@@ -82248,13 +82251,13 @@
     </row>
     <row r="733">
       <c r="A733" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B733" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="C733" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="D733" s="2"/>
       <c r="E733" t="s" s="2">
@@ -82351,13 +82354,13 @@
     </row>
     <row r="734">
       <c r="A734" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B734" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C734" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="D734" s="2"/>
       <c r="E734" t="s" s="2">
@@ -82397,7 +82400,7 @@
       </c>
       <c r="R734" s="2"/>
       <c r="S734" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="T734" t="s" s="2">
         <v>75</v>
@@ -82456,13 +82459,13 @@
     </row>
     <row r="735">
       <c r="A735" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B735" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C735" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="D735" s="2"/>
       <c r="E735" t="s" s="2">
@@ -82485,7 +82488,7 @@
         <v>75</v>
       </c>
       <c r="L735" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="M735" t="s" s="2">
         <v>1002</v>
@@ -82559,13 +82562,13 @@
     </row>
     <row r="736">
       <c r="A736" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B736" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="C736" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="D736" s="2"/>
       <c r="E736" t="s" s="2">
@@ -82664,13 +82667,13 @@
     </row>
     <row r="737">
       <c r="A737" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B737" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="C737" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D737" s="2"/>
       <c r="E737" t="s" s="2">
@@ -82769,13 +82772,13 @@
     </row>
     <row r="738">
       <c r="A738" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B738" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="C738" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="D738" s="2"/>
       <c r="E738" t="s" s="2">
@@ -82874,13 +82877,13 @@
     </row>
     <row r="739">
       <c r="A739" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B739" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="C739" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="D739" s="2"/>
       <c r="E739" t="s" s="2">
@@ -82979,7 +82982,7 @@
     </row>
     <row r="740">
       <c r="A740" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B740" t="s" s="2">
         <v>1174</v>
@@ -83086,7 +83089,7 @@
     </row>
     <row r="741">
       <c r="A741" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B741" t="s" s="2">
         <v>1181</v>
@@ -83118,7 +83121,7 @@
         <v>1182</v>
       </c>
       <c r="M741" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="N741" t="s" s="2">
         <v>1184</v>
@@ -83189,7 +83192,7 @@
     </row>
     <row r="742">
       <c r="A742" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B742" t="s" s="2">
         <v>1185</v>
@@ -83221,7 +83224,7 @@
         <v>258</v>
       </c>
       <c r="M742" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="N742" t="s" s="2">
         <v>1187</v>
@@ -83294,7 +83297,7 @@
     </row>
     <row r="743">
       <c r="A743" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B743" t="s" s="2">
         <v>1190</v>
@@ -83397,7 +83400,7 @@
     </row>
     <row r="744">
       <c r="A744" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B744" t="s" s="2">
         <v>1191</v>
@@ -83502,7 +83505,7 @@
     </row>
     <row r="745">
       <c r="A745" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B745" t="s" s="2">
         <v>1192</v>
@@ -83609,7 +83612,7 @@
     </row>
     <row r="746">
       <c r="A746" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B746" t="s" s="2">
         <v>1193</v>
@@ -83716,7 +83719,7 @@
     </row>
     <row r="747">
       <c r="A747" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B747" t="s" s="2">
         <v>1200</v>
@@ -83825,7 +83828,7 @@
     </row>
     <row r="748">
       <c r="A748" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B748" t="s" s="2">
         <v>1207</v>
@@ -83930,7 +83933,7 @@
     </row>
     <row r="749">
       <c r="A749" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B749" t="s" s="2">
         <v>1211</v>
@@ -83959,10 +83962,10 @@
         <v>75</v>
       </c>
       <c r="L749" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="M749" t="s" s="2">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="N749" t="s" s="2">
         <v>1214</v>
@@ -84033,7 +84036,7 @@
     </row>
     <row r="750">
       <c r="A750" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B750" t="s" s="2">
         <v>1215</v>

--- a/cp-short-description/ig/all-profiles.xlsx
+++ b/cp-short-description/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T15:53:08+00:00</t>
+    <t>2026-06-25T16:02:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -915,7 +915,7 @@
     <t>DocumentReference.description</t>
   </si>
   <si>
-    <t>Description du document source, lisible par l'homme correspondant au commentaire associé au document</t>
+    <t>Description du document source, lisible par l'homme, correspondant au commentaire associé au document</t>
   </si>
   <si>
     <t>Human-readable description of the source document.</t>
